--- a/clients/healthcare-demo-new/19-template-instantiation-source-corpus/01-template-workbooks/HC_SOURCE_REQUEST_LIST.xlsx
+++ b/clients/healthcare-demo-new/19-template-instantiation-source-corpus/01-template-workbooks/HC_SOURCE_REQUEST_LIST.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Requests" sheetId="1" r:id="Rbd4628184d4143e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Families" sheetId="2" r:id="R988037002ed24516"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Requests" sheetId="1" r:id="R1d6eac09acaa4c56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Families" sheetId="2" r:id="R51dcb03e134a435a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -646,7 +646,7 @@
         <x:v>4-6 files</x:v>
       </x:c>
       <x:c r="C2" s="11" t="n">
-        <x:v>1520</x:v>
+        <x:v>1670</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
         <x:v>Applications/platforms plus owner, criticality and lifecycle</x:v>
